--- a/per-stock/POET/financials.xlsx
+++ b/per-stock/POET/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2438797568</v>
+        <v>2097034112</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1802051712</v>
+        <v>1438418688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -577,10 +586,8 @@
           <t>Forward P/E</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Infinity</t>
-        </is>
+      <c r="B9" t="n">
+        <v>-71.47059</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -595,7 +602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2268.9338</v>
+        <v>1485.6841</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -625,7 +632,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-41.7443</v>
+        <v>-35.4997</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -655,7 +662,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.6158400000000001</v>
+        <v>-0.33943</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -670,7 +677,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.753</v>
+        <v>2.019</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -685,7 +692,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>313398304</v>
+        <v>429136448</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -700,7 +707,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7066198</v>
+        <v>7020600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -715,11 +722,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>77321920</v>
+        <v>-36392420</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -730,7 +737,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>152711182</v>
+        <v>172595406</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -745,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15.97</v>
+        <v>12.15</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -789,6 +796,453 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D52</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C52</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B52</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B45:E45)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D42</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C42</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B42</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B35:E35)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D9</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C9</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B9</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B9:E9)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B5:E5)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D2/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C2/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1850,13 +2304,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1866,6 +2320,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1876,30 +2331,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -1921,12 +2381,13 @@
         <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>2307445.65</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1944,12 +2405,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1958,21 +2420,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-12942167</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-10836762</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-7672960</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-7430954</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-8281759</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-10462303</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1981,21 +2444,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>1602298</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-30882501</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-772621</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-9008682</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>15382971</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-19290050</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2004,21 +2468,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>1602298</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-30882501</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-772621</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-9008682</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>15382971</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-19290050</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2027,21 +2492,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-12344086</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-42671682</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-9369714</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-17263375</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>6341558</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-30259239</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2050,21 +2516,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>957700</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>903513</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>892704</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>792814</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>726868</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>475281</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2073,21 +2540,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>-11339869</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>-41719263</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>-8445581</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>-16439636</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>7101212</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>-29752353</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2096,21 +2564,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-12297569</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-42622776</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-9338285</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-17232450</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>6374344</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-30227634</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2119,21 +2588,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-3299017</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-4681142</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-1847701</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-1333389</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-509588</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-6533404</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2142,21 +2612,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>46517</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>48906</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>31429</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>30925</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>32786</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>31605</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2165,21 +2636,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-13946384</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-11789181</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-8597093</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-8254693</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-6733967.35</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-10969189</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2188,21 +2660,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-12344086</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-42671682</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-9369714</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-17263375</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>6341558</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-30259239</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2211,21 +2684,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>15121047</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>9952205</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>8036833</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>7723081</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>9226367</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>4968967</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2234,21 +2708,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>122337</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>144720</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>78421</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>193585</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>83559</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>62863</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2257,21 +2732,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-17870158</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-14243239</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-9554671</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>-8757076</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-9536409</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-11441734</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2279,18 +2755,21 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n">
+      <c r="B18" s="3" t="n">
+        <v>147523126</v>
+      </c>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n">
         <v>89825550</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>81053634</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>78238788</v>
       </c>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n">
         <v>65175436</v>
       </c>
     </row>
@@ -2300,18 +2779,21 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n">
+      <c r="B19" s="3" t="n">
+        <v>147523126</v>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n">
         <v>89825550</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>81053634</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>77538957</v>
       </c>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n">
         <v>65175436</v>
       </c>
     </row>
@@ -2321,18 +2803,21 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n">
+      <c r="B20" s="3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
         <v>-0.1</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-0.21</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n">
+      <c r="F20" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n">
         <v>-0.2</v>
       </c>
     </row>
@@ -2342,18 +2827,21 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n">
+      <c r="B21" s="3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
         <v>-0.1</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-0.21</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>0.08</v>
       </c>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n">
         <v>-0.2</v>
       </c>
     </row>
@@ -2364,21 +2852,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-12344086</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-42671682</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-9369714</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-17263375</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>6341558</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-30259239</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2387,21 +2876,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-12344086</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-42671682</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-9369714</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-17263375</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>6341558</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-30259239</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2410,21 +2900,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-12344086</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-42671682</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-9369714</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-17263375</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>6341558</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-30259239</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2433,21 +2924,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-12344086</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-42671682</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-9369714</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-17263375</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>6341558</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-30259239</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2456,21 +2948,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-12344086</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-42671682</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-9369714</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-17263375</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>6341558</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-30259239</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2479,21 +2972,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-12344086</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-42671682</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-9369714</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-17263375</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>6341558</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-30259239</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2502,21 +2996,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>5572589</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-28379537</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>216386</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-8475374</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>15910753</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-18785900</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2525,21 +3020,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>3970291</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>2502964</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>989007</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>533308</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>527782</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>504150</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2551,10 +3047,11 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F30" s="3" t="n"/>
       <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2565,21 +3062,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>1602298</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-30882501</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-772621</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-9008682</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>15382971</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-12444661</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2588,21 +3086,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-3299017</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-4681142</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-1847701</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-1333389</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-509588</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-6533404</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2611,21 +3110,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>3252500</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>4632236</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>1816272</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>1302464</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>476802</v>
       </c>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n">
-        <v>1319392</v>
-      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2634,21 +3134,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>46517</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>48906</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>31429</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>30925</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>32786</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>31605</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2657,21 +3158,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-14617658</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-9611003</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-7738399</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-7454612</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-9059607</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-4939935</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2680,21 +3182,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>15121047</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>9952205</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>8036833</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>7723081</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>9226367</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>4968967</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2703,21 +3206,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>957700</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>903513</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>892704</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>792814</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>726868</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>475281</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2726,21 +3230,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>957700</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>903513</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>892704</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>792814</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>726868</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>475281</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2749,21 +3254,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>5840334</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>5345349</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>4472495</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>3752352</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>4514107</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>4015734</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2772,21 +3278,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>8323013</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>3703343</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>2671634</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>3177915</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>3985392</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>477952</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2795,21 +3302,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>8323013</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>3703343</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>2671634</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>3177915</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>3985392</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>477952</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2818,21 +3326,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>2007747</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>1335798</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>790110</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>1378776</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>1090681</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-1170738</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2841,21 +3350,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>122337</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>144720</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>78421</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>193585</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>83559</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>62863</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2864,21 +3374,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>6192929</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>2222825</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>1803103</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>1605554</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>2811152</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>1585827</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2887,21 +3398,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>503389</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>341202</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>298434</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>268469</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>166760</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>29032</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2910,28 +3422,29 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>503389</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>341202</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>298434</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>268469</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>166760</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>29032</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4269,7 +4782,1477 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>152893604</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>132021526</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>91010598</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>85265009</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>78074707</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>152893604</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>132021526</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>91010598</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>85265009</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>78074707</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>7020600</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>7066198</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>7284108</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>7326755</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>7322817</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>448109170</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>183232897</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>65857464</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>48760360</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>31873175</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>454443600</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>189589272</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>72938174</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>55865406</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>38956211</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>418810220</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>170708559</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>52925789</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>35330020</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>18780142</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>448109170</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>183232897</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>65857464</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>48760360</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>31873175</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1220600</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1266198</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>784108</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>826755</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>822817</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>448643600</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>183789272</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>66438174</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>49365406</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>32456211</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>448643600</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>183789272</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>66438174</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>49365406</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>32456211</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>448643600</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>183789272</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>66438174</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>49365406</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>32456211</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>448643600</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>183789272</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>66438174</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>49365406</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>32456211</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Other Equity Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>162044130</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>30599602</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>45765710</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>29219025</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>9343000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-2446012</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-2121883</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-2176173</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-348592</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-1784257</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-2446012</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-2121883</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-2176173</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-348592</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-1784257</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-309438420</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-297094334</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-291278379</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-281908665</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-264645290</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>12397616</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>9329724</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>58979770</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>58513941</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>59179629</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>586086286</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>443076163</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>255147246</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>243889697</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>230363129</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>586086286</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>443076163</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>255147246</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>243889697</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>230363129</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>13128261</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>144783166</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>41395495</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>40310064</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>32417199</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>955344</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1029894</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>636231</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>678878</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>568613</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>955344</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1029894</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>636231</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>678878</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>568613</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>955344</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1029894</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>636231</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>678878</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>568613</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>12172917</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>143753272</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>40759264</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>39631186</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>31848586</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>2584759</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>135631585</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>30599601</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>29328610</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>20342530</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>247505</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>445840</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>619002</v>
+      </c>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n">
+        <v>276072</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>247505</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>445840</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>619002</v>
+      </c>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n">
+        <v>276072</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>6065256</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>6036304</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>6647877</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>6647877</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>6754204</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>265256</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>236304</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>147877</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>147877</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>254204</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>3275397</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1639543</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>2892784</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>3654699</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>4475780</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>2516951</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>403333</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>1274500</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>827821</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>417439</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>758446</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>1236210</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1618284</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>2826878</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>4058341</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>758446</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1236210</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1618284</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>2826878</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>4058341</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>461771861</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>328572438</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>107833669</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>89675470</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>64873410</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>30788724</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>14110607</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>14148616</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>14714264</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>14244682</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Non Current Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>208125</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>208125</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>220347</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>115681</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>117192</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Non Current Note Receivables</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>15194384</v>
+      </c>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>534430</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>556375</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>580710</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>605046</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>583036</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>534430</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>556375</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>580710</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>605046</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>583036</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>14851785</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>13346107</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>13347559</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>13993537</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>13544454</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>-11197873</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>-10262108</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>-9382941</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>-8535368</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>-7767081</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>26049658</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>23608215</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>22730500</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>22528905</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>21311535</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1640124</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>991515</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>986123</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>1004840</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>924348</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>2445811</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>1266463</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1230508</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>1446543</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>4293554</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>20069812</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>19458642</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>19133623</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>18690240</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>14739353</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>1893911</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>1891595</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>1380246</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>1387282</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>1354280</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>430983137</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>314461831</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>93685053</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>74961206</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>50628728</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>1006305</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>854640</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>370550</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>407496</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>693307</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>840390</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>208888</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>578598</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>1500706</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1293451</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Taxes Receivable</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>550022</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>208888</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>453519</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>1500706</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1293451</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>290368</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>125079</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>429136442</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>313398303</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>92735905</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>73053004</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>48641970</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>412599049</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>273439102</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>79221458</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>60688044</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>32741545</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>16537393</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>39959201</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>13514447</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>12364960</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>15900425</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>9431265</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>38199492</v>
+      </c>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n">
+        <v>15272677</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>25382406</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>7106128</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>1759709</v>
+      </c>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n">
+        <v>21871082</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>16400493</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5405,13 +7388,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5421,6 +7404,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5431,30 +7415,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -5467,21 +7456,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-11244498</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-10855894</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-3179489</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-9850866</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-9502025</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-12679773</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5490,21 +7480,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-93902</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-765438</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-58517</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-64159</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-35289</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-46285</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5513,21 +7504,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>142591249</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>231764506</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>25851464</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>31273000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>4352685</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>25782860</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5535,22 +7527,23 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n">
+      <c r="B5" s="3" t="n">
+        <v>-2434925</v>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n">
         <v>-406439</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-2111832</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-522523</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="G5" s="3" t="n">
         <v>-3990337</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>-1022635</v>
-      </c>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5559,21 +7552,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>16537393</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>39959201</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>13514447</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>12364960</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>15900425</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>37143759</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5582,21 +7576,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>39959201</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>13514447</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>12364960</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>15900425</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>37143759</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>41782899</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5605,21 +7600,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>-320326</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>1340774</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>-1221930</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>588940</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>37513</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>-1013074</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5628,21 +7624,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>-23101482</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>25103980</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>2371417</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>-4124405</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>-21280847</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>-3626066</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5651,21 +7648,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>142497347</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>230999068</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>25792947</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>31208841</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>4317396</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>25736575</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5674,21 +7672,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>142497347</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>230999068</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>25792947</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>31208841</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>4317396</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>25736575</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5697,21 +7696,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>142591249</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>231764506</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>25851464</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>31273000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>4352685</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>25782860</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5720,21 +7720,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>142591249</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>231764506</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>25851464</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>31273000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>4352685</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>25782860</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5743,21 +7744,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-93902</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-765438</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-58517</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-64159</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-35289</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-46285</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5767,14 +7769,15 @@
       </c>
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="3" t="n"/>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5784,14 +7787,15 @@
       </c>
       <c r="B16" s="3" t="n"/>
       <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="3" t="n"/>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5800,21 +7804,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-93902</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-65438</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-58517</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>-64159</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-35289</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-24391</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5823,21 +7828,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-93902</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-65438</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-58517</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-64159</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-35289</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-24391</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5846,21 +7852,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-156789256</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-194300044</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-20648480</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-27594212</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-16618741</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-20673205</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5869,604 +7876,675 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-156789256</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-194300044</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-20648480</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-27594212</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-16618741</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-20673205</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Net Investment Purchase And Sale</t>
+          <t>Net Other Investing Changes</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-195039194</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>-20242041</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>-25482380</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-16096218</v>
-      </c>
+        <v>-15194384</v>
+      </c>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Purchase Of Investment</t>
+          <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-209899085</v>
+        <v>-139159947</v>
       </c>
       <c r="C22" s="3" t="n">
+        <v>-195039194</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>-20242041</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-25482380</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-16096218</v>
       </c>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Net Intangibles Purchase And Sale</t>
+          <t>Sale Of Investment</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>-46537</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>28000000</v>
+      </c>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n">
-        <v>-68087</v>
+        <v>0</v>
       </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Purchase Of Intangibles</t>
+          <t>Purchase Of Investment</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-1</v>
+        <v>-167159947</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1</v>
+        <v>-209899085</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-46537</v>
+        <v>-20242041</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0</v>
+        <v>-25482380</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-68087</v>
+        <v>-16096218</v>
       </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Net PPE Purchase And Sale</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>739151</v>
-      </c>
+          <t>Net Intangibles Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
       <c r="C25" s="3" t="n">
-        <v>-406440</v>
+        <v>-1</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-2065295</v>
+        <v>1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-522523</v>
+        <v>-46537</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-3922250</v>
-      </c>
-      <c r="G25" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-68087</v>
+      </c>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Purchase Of PPE</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>739151</v>
-      </c>
+          <t>Purchase Of Intangibles</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
       <c r="C26" s="3" t="n">
-        <v>-406440</v>
+        <v>-1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-2065295</v>
+        <v>1</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-522523</v>
+        <v>-46537</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-3922250</v>
-      </c>
-      <c r="G26" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-68087</v>
+      </c>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Operating Cash Flow</t>
+          <t>Net PPE Purchase And Sale</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-11595044</v>
+        <v>-2434925</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2773050</v>
+        <v>739151</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7739034</v>
+        <v>-406440</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-8979502</v>
+        <v>-2065295</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-8689436</v>
+        <v>-522523</v>
       </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Operating Activities</t>
+          <t>Purchase Of PPE</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-11595044</v>
+        <v>-2434925</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-2773050</v>
+        <v>739151</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-7739034</v>
+        <v>-406440</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-8979502</v>
+        <v>-2065295</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>-8689436</v>
+        <v>-522523</v>
       </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Change In Working Capital</t>
+          <t>Operating Cash Flow</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3396181</v>
+        <v>-8809573</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1429222</v>
+        <v>-11595044</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>111422</v>
+        <v>-2773050</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1514892</v>
+        <v>-7739034</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>379290</v>
+        <v>-8979502</v>
       </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Change In Other Working Capital</t>
+          <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-170598</v>
-      </c>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
+        <v>-8809573</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-11595044</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>-2773050</v>
+      </c>
       <c r="E30" s="3" t="n">
-        <v>274926</v>
-      </c>
-      <c r="F30" s="3" t="n"/>
+        <v>-7739034</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>-8979502</v>
+      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Change In Payables And Accrued Expense</t>
+          <t>Change In Working Capital</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-3011741</v>
+        <v>645807</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-344824</v>
+        <v>-3396181</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>482503</v>
+        <v>1429222</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-1572732</v>
+        <v>111422</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>703303</v>
+        <v>-1514892</v>
       </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Change In Prepaid Assets</t>
+          <t>Change In Other Working Capital</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-346178</v>
+        <v>-199898</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1289627</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>-96155</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>-217086</v>
-      </c>
+        <v>-170598</v>
+      </c>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n">
-        <v>-316756</v>
+        <v>274926</v>
       </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Change In Receivables</t>
+          <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>132336</v>
-      </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
+        <v>1631210</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>-3011741</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>-344824</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>482503</v>
+      </c>
       <c r="F33" s="3" t="n">
-        <v>-7257</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-1572732</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Changes In Account Receivables</t>
+          <t>Change In Prepaid Assets</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>132336</v>
-      </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
+        <v>-492934</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>-346178</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>1289627</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-96155</v>
+      </c>
       <c r="F34" s="3" t="n">
-        <v>-7257</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-217086</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Other Non Cash Items</t>
+          <t>Change In Receivables</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>449469</v>
+        <v>-292571</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-159512</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>245129</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>8142</v>
-      </c>
+        <v>132336</v>
+      </c>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n">
-        <v>6865524</v>
-      </c>
-      <c r="G35" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>-7257</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Stock Based Compensation</t>
+          <t>Changes In Account Receivables</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>2235188</v>
+        <v>-292571</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1864589</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>1165482</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>841793</v>
-      </c>
+        <v>132336</v>
+      </c>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n">
-        <v>1404995</v>
-      </c>
-      <c r="G36" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>-7257</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
+          <t>Other Non Cash Items</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>903513</v>
+        <v>46538</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>892704</v>
+        <v>449469</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>792814</v>
+        <v>-159512</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>726868</v>
+        <v>245129</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>475281</v>
+        <v>8142</v>
       </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Stock Based Compensation</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>903513</v>
+        <v>3486766</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>892704</v>
+        <v>2235188</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>792814</v>
+        <v>1864589</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>726868</v>
+        <v>1165482</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>475281</v>
+        <v>841793</v>
       </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Amortization Cash Flow</t>
+          <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>24336</v>
+        <v>957700</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>24335</v>
+        <v>903513</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>24527</v>
+        <v>892704</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>23672</v>
+        <v>792814</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>24228</v>
+        <v>726868</v>
       </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Amortization Of Intangibles</t>
+          <t>Depreciation And Amortization</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>24336</v>
+        <v>957700</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>24335</v>
+        <v>903513</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>24527</v>
+        <v>892704</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>23672</v>
+        <v>792814</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>24228</v>
+        <v>726868</v>
       </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Amortization Cash Flow</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>879177</v>
+        <v>21945</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>868369</v>
+        <v>24336</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>768287</v>
+        <v>24335</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>703196</v>
+        <v>24527</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>451053</v>
+        <v>23672</v>
       </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Operating Gains Losses</t>
+          <t>Amortization Of Intangibles</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>30884649</v>
+        <v>21945</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2569661</v>
+        <v>24336</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7209494</v>
+        <v>24335</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>-15382971</v>
+        <v>24527</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>12444713</v>
+        <v>23672</v>
       </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Earnings Losses From Equity Investments</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>935755</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>879177</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>868369</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>768287</v>
+      </c>
       <c r="F43" s="3" t="n">
-        <v>0</v>
+        <v>703196</v>
       </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Gain Loss On Investment Securities</t>
+          <t>Operating Gains Losses</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>30689590</v>
+        <v>-1602298</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2414223</v>
+        <v>30884649</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>7559991</v>
+        <v>2569661</v>
       </c>
       <c r="E44" s="3" t="n">
+        <v>7209494</v>
+      </c>
+      <c r="F44" s="3" t="n">
         <v>-15382971</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>12444661</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Net Foreign Currency Exchange Gain Loss</t>
+          <t>Earnings Losses From Equity Investments</t>
         </is>
       </c>
       <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n">
-        <v>155438</v>
-      </c>
+      <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="n"/>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n"/>
       <c r="G45" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Gain Loss On Investment Securities</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>-1602298</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>30689590</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>2414223</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>7559991</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>-15382971</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Net Foreign Currency Exchange Gain Loss</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n">
+        <v>155438</v>
+      </c>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
+      <c r="B48" s="3" t="n">
+        <v>-12344086</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>-42671682</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>-9369714</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>-17263375</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>6341558</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>-30259239</v>
-      </c>
-      <c r="G46" s="3" t="n"/>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6497,6 +8575,30 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FY Summary</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>'Gross Profit' not found in statements — left blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FY Summary</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>'Net Debt' not found in statements — left blank</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
